--- a/stacked_model/results/validation/validation_summary.xlsx
+++ b/stacked_model/results/validation/validation_summary.xlsx
@@ -562,40 +562,40 @@
         <v>1900</v>
       </c>
       <c r="H2" t="n">
-        <v>3.432880675296015</v>
+        <v>3.443256318928505</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3817542260411853</v>
+        <v>0.37447001959853</v>
       </c>
       <c r="J2" t="n">
-        <v>4.582308598926443</v>
+        <v>4.603525284041718</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5112934295468461</v>
+        <v>0.5008180569741756</v>
       </c>
       <c r="L2" t="n">
-        <v>0.772869326990449</v>
+        <v>0.7725109785490014</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06071646363784602</v>
+        <v>0.05648824630631295</v>
       </c>
       <c r="N2" t="n">
-        <v>0.866842105263158</v>
+        <v>0.8689473684210527</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05535642480099032</v>
+        <v>0.0563884711222476</v>
       </c>
       <c r="P2" t="n">
-        <v>3.126582970936398</v>
+        <v>3.193334177728245</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4932695266230907</v>
+        <v>0.6271261990191498</v>
       </c>
       <c r="R2" t="n">
-        <v>-117.5383180775372</v>
+        <v>-117.4092706075031</v>
       </c>
       <c r="S2" t="n">
-        <v>3.962128563784979</v>
+        <v>4.481342632593394</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -635,40 +635,40 @@
         <v>1900</v>
       </c>
       <c r="H3" t="n">
-        <v>3.434099098131329</v>
+        <v>3.443519805465228</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3809099008571974</v>
+        <v>0.3747278172905925</v>
       </c>
       <c r="J3" t="n">
-        <v>4.583844104862155</v>
+        <v>4.60370779712007</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5104247323576646</v>
+        <v>0.5009692811106323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7727342490364975</v>
+        <v>0.7724913615115532</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06062929920386277</v>
+        <v>0.05650392716020053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8742105263157895</v>
+        <v>0.8757894736842107</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05350774476190659</v>
+        <v>0.05237315719479097</v>
       </c>
       <c r="P3" t="n">
-        <v>3.08771418107404</v>
+        <v>3.04977555071663</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6307155765447575</v>
+        <v>0.328485607930392</v>
       </c>
       <c r="R3" t="n">
-        <v>-117.4315592994587</v>
+        <v>-117.3997209991836</v>
       </c>
       <c r="S3" t="n">
-        <v>4.185994643375805</v>
+        <v>4.508353374855829</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -708,40 +708,40 @@
         <v>1900</v>
       </c>
       <c r="H4" t="n">
-        <v>3.434099096484621</v>
+        <v>3.443520443705095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3809100847031243</v>
+        <v>0.3747289543154171</v>
       </c>
       <c r="J4" t="n">
-        <v>4.583844181084598</v>
+        <v>4.603709179861533</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5104247950657705</v>
+        <v>0.5009709940895716</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7727342424964155</v>
+        <v>0.7724912445534449</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06062930367018866</v>
+        <v>0.05650391094461293</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8742105263157895</v>
+        <v>0.8757894736842107</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05350774476190659</v>
+        <v>0.05237315719479097</v>
       </c>
       <c r="P4" t="n">
-        <v>3.087743019916063</v>
+        <v>3.049784634498774</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6308677110760262</v>
+        <v>0.3285048979265214</v>
       </c>
       <c r="R4" t="n">
-        <v>-117.4315592993045</v>
+        <v>-117.3997210017015</v>
       </c>
       <c r="S4" t="n">
-        <v>4.185994643369099</v>
+        <v>4.5083533768298</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>1e-06</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
@@ -781,40 +781,40 @@
         <v>1900</v>
       </c>
       <c r="H5" t="n">
-        <v>3.457110590144142</v>
+        <v>3.466968679090963</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4490449307875504</v>
+        <v>0.4052435412929845</v>
       </c>
       <c r="J5" t="n">
-        <v>4.612595140747029</v>
+        <v>4.637947152852727</v>
       </c>
       <c r="K5" t="n">
-        <v>0.587454504284259</v>
+        <v>0.5433693492409143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7692051492531198</v>
+        <v>0.7687568292336757</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0686286224882363</v>
+        <v>0.0606380880388891</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8652631578947368</v>
+        <v>0.8742105263157895</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05790938199690138</v>
+        <v>0.05403342537466495</v>
       </c>
       <c r="P5" t="n">
-        <v>3.155544749142379</v>
+        <v>3.061240351787645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.527579734878287</v>
+        <v>0.3307846814051329</v>
       </c>
       <c r="R5" t="n">
-        <v>-117.4323476741037</v>
+        <v>-117.3585269039338</v>
       </c>
       <c r="S5" t="n">
-        <v>4.103928229387479</v>
+        <v>4.500477716705376</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
         <v>50</v>
@@ -854,40 +854,40 @@
         <v>1900</v>
       </c>
       <c r="H6" t="n">
-        <v>3.458454480095515</v>
+        <v>3.479339618324667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4487382402104824</v>
+        <v>0.4163103875751053</v>
       </c>
       <c r="J6" t="n">
-        <v>4.614247264107965</v>
+        <v>4.656564089468655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5870166113878141</v>
+        <v>0.5748975750729397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7690543916547915</v>
+        <v>0.7666466026211372</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06859519558418599</v>
+        <v>0.06362838395544883</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8726315789473685</v>
+        <v>0.866842105263158</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05559844074386812</v>
+        <v>0.05953871334323512</v>
       </c>
       <c r="P6" t="n">
-        <v>3.104090027432973</v>
+        <v>3.232129648954282</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6389668365809775</v>
+        <v>0.6546710239680206</v>
       </c>
       <c r="R6" t="n">
-        <v>-117.3252903603542</v>
+        <v>-117.3268295568308</v>
       </c>
       <c r="S6" t="n">
-        <v>4.318329650723205</v>
+        <v>4.541118992618192</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -927,40 +927,40 @@
         <v>1900</v>
       </c>
       <c r="H7" t="n">
-        <v>3.458454218823177</v>
+        <v>3.483909969088897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4487352424135821</v>
+        <v>0.4246595518964142</v>
       </c>
       <c r="J7" t="n">
-        <v>4.614247521194718</v>
+        <v>4.660974224435389</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5870150289264077</v>
+        <v>0.5838047743844124</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7690543899533079</v>
+        <v>0.766149739575976</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06859499507387437</v>
+        <v>0.06442021271485697</v>
       </c>
       <c r="N7" t="n">
         <v>0.8726315789473685</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05559844074386812</v>
+        <v>0.05685523180574305</v>
       </c>
       <c r="P7" t="n">
-        <v>3.104060854518174</v>
+        <v>3.127557529657686</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6388151488641017</v>
+        <v>0.5776619374061419</v>
       </c>
       <c r="R7" t="n">
-        <v>-117.3252903615404</v>
+        <v>-117.2591759224323</v>
       </c>
       <c r="S7" t="n">
-        <v>4.318329648399748</v>
+        <v>4.672546843451236</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F8" t="n">
         <v>50</v>
@@ -1000,40 +1000,40 @@
         <v>1900</v>
       </c>
       <c r="H8" t="n">
-        <v>3.670820332096605</v>
+        <v>3.709754758002719</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3995629997910594</v>
+        <v>0.358685722928652</v>
       </c>
       <c r="J8" t="n">
-        <v>4.775948621903612</v>
+        <v>4.857123097334653</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5251891246767287</v>
+        <v>0.486977141881412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7524883281363782</v>
+        <v>0.7468854196085399</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06821914360377973</v>
+        <v>0.05963599165562142</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8810526315789473</v>
+        <v>0.8742105263157895</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05296350756498142</v>
+        <v>0.05324295817662904</v>
       </c>
       <c r="P8" t="n">
-        <v>2.980169837668918</v>
+        <v>2.998128722408036</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1237890851413548</v>
+        <v>0.1158808755357519</v>
       </c>
       <c r="R8" t="n">
-        <v>-122.3662119709173</v>
+        <v>-122.1405651078226</v>
       </c>
       <c r="S8" t="n">
-        <v>4.011924055063536</v>
+        <v>3.850572894087481</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F9" t="n">
         <v>50</v>
@@ -1073,40 +1073,40 @@
         <v>1900</v>
       </c>
       <c r="H9" t="n">
-        <v>3.670820395704882</v>
+        <v>3.709754976117901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3995636388995941</v>
+        <v>0.358685335242283</v>
       </c>
       <c r="J9" t="n">
-        <v>4.775948760854281</v>
+        <v>4.857123374279075</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5251903644162843</v>
+        <v>0.4869758860048832</v>
       </c>
       <c r="L9" t="n">
-        <v>0.752488301954079</v>
+        <v>0.7468853374680779</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06821923166181193</v>
+        <v>0.0596362513565185</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8810526315789473</v>
+        <v>0.8615789473684211</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05296350756498142</v>
+        <v>0.05671834799186137</v>
       </c>
       <c r="P9" t="n">
-        <v>2.98017036892907</v>
+        <v>3.005838608488958</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1237900792065926</v>
+        <v>0.1271674381191973</v>
       </c>
       <c r="R9" t="n">
-        <v>-122.3662119712071</v>
+        <v>-122.1405650914613</v>
       </c>
       <c r="S9" t="n">
-        <v>4.011924055071219</v>
+        <v>3.850572894364687</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
@@ -1146,40 +1146,40 @@
         <v>1900</v>
       </c>
       <c r="H10" t="n">
-        <v>3.671594150557759</v>
+        <v>3.709755122701998</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4008066414970204</v>
+        <v>0.358685014471916</v>
       </c>
       <c r="J10" t="n">
-        <v>4.776648927858435</v>
+        <v>4.85712349434068</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5261482362909006</v>
+        <v>0.4869767649416206</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7523780846650052</v>
+        <v>0.7468853778091347</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0685209380203316</v>
+        <v>0.05963597538359333</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8705263157894736</v>
+        <v>0.8742105263157895</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05391559411127086</v>
+        <v>0.05324295817662904</v>
       </c>
       <c r="P10" t="n">
-        <v>2.985768376302781</v>
+        <v>2.9981282035874</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1333527887281296</v>
+        <v>0.1158797563129038</v>
       </c>
       <c r="R10" t="n">
-        <v>-122.3663589612465</v>
+        <v>-122.140565102521</v>
       </c>
       <c r="S10" t="n">
-        <v>4.011686711005654</v>
+        <v>3.850572893695601</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
@@ -1219,40 +1219,40 @@
         <v>1900</v>
       </c>
       <c r="H11" t="n">
-        <v>3.677320917928911</v>
+        <v>3.709755171468339</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4389954582370614</v>
+        <v>0.3586858033445913</v>
       </c>
       <c r="J11" t="n">
-        <v>4.781164466452669</v>
+        <v>4.857123694841752</v>
       </c>
       <c r="K11" t="n">
-        <v>0.583129904906736</v>
+        <v>0.4869775985599932</v>
       </c>
       <c r="L11" t="n">
-        <v>0.751245479743699</v>
+        <v>0.7468853500064122</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07385870867329235</v>
+        <v>0.05963608800519114</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8815789473684209</v>
+        <v>0.8615789473684211</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05454367717498837</v>
+        <v>0.05671834799186137</v>
       </c>
       <c r="P11" t="n">
-        <v>2.981541677546098</v>
+        <v>3.005838788492237</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1292963713287512</v>
+        <v>0.1271669650004434</v>
       </c>
       <c r="R11" t="n">
-        <v>-122.3317478004683</v>
+        <v>-122.1405651003559</v>
       </c>
       <c r="S11" t="n">
-        <v>4.011489526008674</v>
+        <v>3.850572895599543</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1292,40 +1292,40 @@
         <v>1900</v>
       </c>
       <c r="H12" t="n">
-        <v>3.677321599751672</v>
+        <v>3.726592820092359</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4389973508746383</v>
+        <v>0.3696168453153781</v>
       </c>
       <c r="J12" t="n">
-        <v>4.781165064657404</v>
+        <v>4.885616616317524</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5831319988515832</v>
+        <v>0.5082680428752574</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7512454037644128</v>
+        <v>0.7437645315371816</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07385890952812468</v>
+        <v>0.06159917501785264</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8815789473684209</v>
+        <v>0.8731578947368422</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05454367717498837</v>
+        <v>0.05281653859187437</v>
       </c>
       <c r="P12" t="n">
-        <v>2.981541446415382</v>
+        <v>3.001018774913535</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1292958990526612</v>
+        <v>0.1147867811203453</v>
       </c>
       <c r="R12" t="n">
-        <v>-122.3317477996185</v>
+        <v>-122.1368894175959</v>
       </c>
       <c r="S12" t="n">
-        <v>4.011489526529976</v>
+        <v>3.848514315289827</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01</v>
+        <v>1e-06</v>
       </c>
       <c r="F13" t="n">
         <v>50</v>
@@ -1365,40 +1365,40 @@
         <v>1900</v>
       </c>
       <c r="H13" t="n">
-        <v>3.682517463270433</v>
+        <v>3.726593073091666</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4408544061738226</v>
+        <v>0.3696167492503292</v>
       </c>
       <c r="J13" t="n">
-        <v>4.790689556677747</v>
+        <v>4.885616791706679</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5863048546268791</v>
+        <v>0.5082679120012855</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7495205024284651</v>
+        <v>0.7437645271480272</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07852698652065895</v>
+        <v>0.06159908267756254</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8705263157894736</v>
+        <v>0.8731578947368422</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05647612619011706</v>
+        <v>0.05281653859187437</v>
       </c>
       <c r="P13" t="n">
-        <v>2.988752783737266</v>
+        <v>3.001019506540491</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1391451871592149</v>
+        <v>0.1147879577095422</v>
       </c>
       <c r="R13" t="n">
-        <v>-122.3059195239165</v>
+        <v>-122.1368894175088</v>
       </c>
       <c r="S13" t="n">
-        <v>4.043449691463575</v>
+        <v>3.848514315254851</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F14" t="n">
         <v>50</v>
@@ -1438,40 +1438,40 @@
         <v>1900</v>
       </c>
       <c r="H14" t="n">
-        <v>3.869695260128584</v>
+        <v>3.781730755886398</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6614971667057515</v>
+        <v>0.6421504607242831</v>
       </c>
       <c r="J14" t="n">
-        <v>5.831125661760646</v>
+        <v>5.678499689998842</v>
       </c>
       <c r="K14" t="n">
-        <v>1.463414335233759</v>
+        <v>1.45241162822555</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8131120643046106</v>
+        <v>0.8205451962565785</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1054519059712822</v>
+        <v>0.1021510297250552</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8684210526315791</v>
+        <v>0.8847368421052632</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07270330678877336</v>
+        <v>0.06970415503730491</v>
       </c>
       <c r="P14" t="n">
-        <v>3.233243797230067</v>
+        <v>3.150145626752687</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4147755760654275</v>
+        <v>0.2862200660165098</v>
       </c>
       <c r="R14" t="n">
-        <v>-92.96350938255723</v>
+        <v>-93.19370490582287</v>
       </c>
       <c r="S14" t="n">
-        <v>8.131850992794961</v>
+        <v>8.152461095298786</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -1503,40 +1503,40 @@
         <v>1900</v>
       </c>
       <c r="H15" t="n">
-        <v>3.880691463914166</v>
+        <v>3.781730819754383</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6652731973711774</v>
+        <v>0.6421505297902222</v>
       </c>
       <c r="J15" t="n">
-        <v>5.848690223450014</v>
+        <v>5.678499830461164</v>
       </c>
       <c r="K15" t="n">
-        <v>1.468938699423261</v>
+        <v>1.452411696371051</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8121401444958813</v>
+        <v>0.8205451884644828</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1053347451528176</v>
+        <v>0.1021510253132246</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8826315789473683</v>
+        <v>0.8847368421052632</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06792141791670174</v>
+        <v>0.06970415503730491</v>
       </c>
       <c r="P15" t="n">
-        <v>3.171975169520583</v>
+        <v>3.150148976798064</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2942978670779252</v>
+        <v>0.2862252188008217</v>
       </c>
       <c r="R15" t="n">
-        <v>-92.95479465443761</v>
+        <v>-93.19370490589679</v>
       </c>
       <c r="S15" t="n">
-        <v>8.127283327056023</v>
+        <v>8.152461095332256</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F16" t="n">
         <v>50</v>
@@ -1568,40 +1568,40 @@
         <v>1900</v>
       </c>
       <c r="H16" t="n">
-        <v>3.880691536142448</v>
+        <v>3.786504429129417</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6652731242817281</v>
+        <v>0.6489169951341316</v>
       </c>
       <c r="J16" t="n">
-        <v>5.848690238916125</v>
+        <v>5.696376857724666</v>
       </c>
       <c r="K16" t="n">
-        <v>1.468938684284019</v>
+        <v>1.477479220300409</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8121401438813309</v>
+        <v>0.8193288369469472</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1053347443914457</v>
+        <v>0.1031527234910025</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8826315789473683</v>
+        <v>0.8715789473684211</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06792141791670174</v>
+        <v>0.07145626689032614</v>
       </c>
       <c r="P16" t="n">
-        <v>3.171971484229076</v>
+        <v>3.21041114903842</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2942916433652344</v>
+        <v>0.3772340498713238</v>
       </c>
       <c r="R16" t="n">
-        <v>-92.95479465450211</v>
+        <v>-93.1784359849849</v>
       </c>
       <c r="S16" t="n">
-        <v>8.127283327091485</v>
+        <v>8.143382553930598</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -1633,40 +1633,40 @@
         <v>1900</v>
       </c>
       <c r="H17" t="n">
-        <v>3.938294558845263</v>
+        <v>3.822313993705845</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6864521465517048</v>
+        <v>0.6877575040096144</v>
       </c>
       <c r="J17" t="n">
-        <v>5.93864587207969</v>
+        <v>5.745462982056532</v>
       </c>
       <c r="K17" t="n">
-        <v>1.45804830478359</v>
+        <v>1.482832528485499</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8066334949149474</v>
+        <v>0.8160363935009392</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1050151468291599</v>
+        <v>0.1039222144949702</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8647368421052631</v>
+        <v>0.8689473684210526</v>
       </c>
       <c r="O17" t="n">
-        <v>0.07367078287963913</v>
+        <v>0.07357095792473585</v>
       </c>
       <c r="P17" t="n">
-        <v>3.26153585500976</v>
+        <v>3.245053784659012</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4234301526611098</v>
+        <v>0.4298049984536266</v>
       </c>
       <c r="R17" t="n">
-        <v>-92.88090394897633</v>
+        <v>-93.07681626253216</v>
       </c>
       <c r="S17" t="n">
-        <v>8.097595733086363</v>
+        <v>8.140796726164378</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F18" t="n">
         <v>50</v>
@@ -1698,40 +1698,40 @@
         <v>1900</v>
       </c>
       <c r="H18" t="n">
-        <v>3.938295141680098</v>
+        <v>3.822314241277788</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6864542609557979</v>
+        <v>0.6877586826874507</v>
       </c>
       <c r="J18" t="n">
-        <v>5.938646690773604</v>
+        <v>5.745463455870857</v>
       </c>
       <c r="K18" t="n">
-        <v>1.458050029227966</v>
+        <v>1.482834269731796</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8066334027232115</v>
+        <v>0.8160363316253606</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1050152919718952</v>
+        <v>0.103922341947172</v>
       </c>
       <c r="N18" t="n">
-        <v>0.88</v>
+        <v>0.8826315789473683</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06894371961712872</v>
+        <v>0.07254957309507695</v>
       </c>
       <c r="P18" t="n">
-        <v>3.194643339313186</v>
+        <v>3.181487701061981</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3040886706959394</v>
+        <v>0.3258600715067322</v>
       </c>
       <c r="R18" t="n">
-        <v>-92.88090395030646</v>
+        <v>-93.07681622748819</v>
       </c>
       <c r="S18" t="n">
-        <v>8.097595733221217</v>
+        <v>8.140796736900231</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>1e-06</v>
+        <v>1e-10</v>
       </c>
       <c r="F19" t="n">
         <v>50</v>
@@ -1763,40 +1763,40 @@
         <v>1900</v>
       </c>
       <c r="H19" t="n">
-        <v>3.938296288390266</v>
+        <v>3.822315091914536</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6864542911920775</v>
+        <v>0.6877610048092768</v>
       </c>
       <c r="J19" t="n">
-        <v>5.938648737015545</v>
+        <v>5.745463703924885</v>
       </c>
       <c r="K19" t="n">
-        <v>1.458049381038027</v>
+        <v>1.482834092887398</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8066332743587187</v>
+        <v>0.8160363215695114</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1050152763743381</v>
+        <v>0.1039223279483686</v>
       </c>
       <c r="N19" t="n">
-        <v>0.88</v>
+        <v>0.8826315789473683</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06894371961712872</v>
+        <v>0.07254957309507695</v>
       </c>
       <c r="P19" t="n">
-        <v>3.194648080136794</v>
+        <v>3.181483453815591</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3040958745270748</v>
+        <v>0.3258523237800394</v>
       </c>
       <c r="R19" t="n">
-        <v>-92.88090395072896</v>
+        <v>-93.07681622287423</v>
       </c>
       <c r="S19" t="n">
-        <v>8.097595733356362</v>
+        <v>8.140796738274695</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
@@ -1828,40 +1828,40 @@
         <v>1900</v>
       </c>
       <c r="H20" t="n">
-        <v>4.241557555463249</v>
+        <v>4.19553354053343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.71107258352709</v>
+        <v>0.680133874029153</v>
       </c>
       <c r="J20" t="n">
-        <v>6.092020955586945</v>
+        <v>5.973222427153738</v>
       </c>
       <c r="K20" t="n">
-        <v>1.480047540890516</v>
+        <v>1.41134558896239</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7971520264292173</v>
+        <v>0.8034126470840408</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1109332819397375</v>
+        <v>0.1043822972291243</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8478947368421053</v>
+        <v>0.8673684210526317</v>
       </c>
       <c r="O20" t="n">
-        <v>0.07039015665154243</v>
+        <v>0.07230565582057928</v>
       </c>
       <c r="P20" t="n">
-        <v>3.229902715246915</v>
+        <v>3.188811346733944</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.3457834982924182</v>
+        <v>0.2867443607334661</v>
       </c>
       <c r="R20" t="n">
-        <v>-97.47645457877761</v>
+        <v>-97.72737495188591</v>
       </c>
       <c r="S20" t="n">
-        <v>7.546256350248373</v>
+        <v>7.547853000719799</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -1893,40 +1893,40 @@
         <v>1900</v>
       </c>
       <c r="H21" t="n">
-        <v>4.244666028403588</v>
+        <v>4.195533441819518</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7071111125592207</v>
+        <v>0.6801348280233869</v>
       </c>
       <c r="J21" t="n">
-        <v>6.094289981315016</v>
+        <v>5.973223395891116</v>
       </c>
       <c r="K21" t="n">
-        <v>1.477044070181857</v>
+        <v>1.411347384448408</v>
       </c>
       <c r="L21" t="n">
-        <v>0.797043964117639</v>
+        <v>0.803412547866906</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1108303573592058</v>
+        <v>0.1043825802976856</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8668421052631579</v>
+        <v>0.8673684210526317</v>
       </c>
       <c r="O21" t="n">
-        <v>0.07180549540718342</v>
+        <v>0.07230565582057928</v>
       </c>
       <c r="P21" t="n">
-        <v>3.198741011842143</v>
+        <v>3.188813618139309</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3029457719038903</v>
+        <v>0.2867470424563529</v>
       </c>
       <c r="R21" t="n">
-        <v>-97.47310475702268</v>
+        <v>-97.72737496078261</v>
       </c>
       <c r="S21" t="n">
-        <v>7.543674565185135</v>
+        <v>7.547853003987138</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F22" t="n">
         <v>50</v>
@@ -1958,40 +1958,40 @@
         <v>1900</v>
       </c>
       <c r="H22" t="n">
-        <v>4.244671121998336</v>
+        <v>4.196745735211449</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7071058506176005</v>
+        <v>0.6959562332324236</v>
       </c>
       <c r="J22" t="n">
-        <v>6.09429532278673</v>
+        <v>5.9941923594051</v>
       </c>
       <c r="K22" t="n">
-        <v>1.477039151377521</v>
+        <v>1.423704245645634</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7970437106131461</v>
+        <v>0.8020590840049026</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1108301632076046</v>
+        <v>0.1047867860732239</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8668421052631579</v>
+        <v>0.8521052631578947</v>
       </c>
       <c r="O22" t="n">
-        <v>0.07180549540718342</v>
+        <v>0.0701084983270843</v>
       </c>
       <c r="P22" t="n">
-        <v>3.198739116136922</v>
+        <v>3.226070556457095</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3029421200677613</v>
+        <v>0.3285094337176734</v>
       </c>
       <c r="R22" t="n">
-        <v>-97.4731047646718</v>
+        <v>-97.70057325484892</v>
       </c>
       <c r="S22" t="n">
-        <v>7.543674567494045</v>
+        <v>7.550715739555349</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -2023,40 +2023,40 @@
         <v>1900</v>
       </c>
       <c r="H23" t="n">
-        <v>4.286620365209236</v>
+        <v>4.275525773267599</v>
       </c>
       <c r="I23" t="n">
-        <v>0.706023262673242</v>
+        <v>0.696219299762042</v>
       </c>
       <c r="J23" t="n">
-        <v>6.161112910023</v>
+        <v>6.100282400365196</v>
       </c>
       <c r="K23" t="n">
-        <v>1.442977942224819</v>
+        <v>1.37776855370589</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7927908779211787</v>
+        <v>0.7953482982790269</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1101986207933</v>
+        <v>0.1042717460616921</v>
       </c>
       <c r="N23" t="n">
         <v>0.8610526315789474</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06953159712298883</v>
+        <v>0.0748186417904293</v>
       </c>
       <c r="P23" t="n">
-        <v>3.221090515610791</v>
+        <v>3.219437332801541</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2975773250393094</v>
+        <v>0.295946422618875</v>
       </c>
       <c r="R23" t="n">
-        <v>-97.30129390313978</v>
+        <v>-97.53672070450537</v>
       </c>
       <c r="S23" t="n">
-        <v>7.477158228326291</v>
+        <v>7.51161032432415</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -2088,40 +2088,40 @@
         <v>1900</v>
       </c>
       <c r="H24" t="n">
-        <v>4.30461874523414</v>
+        <v>4.275709365365421</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7155191774415022</v>
+        <v>0.6961604047212788</v>
       </c>
       <c r="J24" t="n">
-        <v>6.197028354871878</v>
+        <v>6.100742720910757</v>
       </c>
       <c r="K24" t="n">
-        <v>1.443947463717196</v>
+        <v>1.377430467092685</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7907261437481716</v>
+        <v>0.7953228108144491</v>
       </c>
       <c r="M24" t="n">
-        <v>0.109747226587782</v>
+        <v>0.1042559933682687</v>
       </c>
       <c r="N24" t="n">
         <v>0.8610526315789474</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06953159712298883</v>
+        <v>0.0748186417904293</v>
       </c>
       <c r="P24" t="n">
-        <v>3.224978283858681</v>
+        <v>3.220998862712821</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2973808480908679</v>
+        <v>0.2954236447563436</v>
       </c>
       <c r="R24" t="n">
-        <v>-97.31113296629063</v>
+        <v>-97.51386009565137</v>
       </c>
       <c r="S24" t="n">
-        <v>7.477395825821525</v>
+        <v>7.507754883702987</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
@@ -2153,40 +2153,40 @@
         <v>1900</v>
       </c>
       <c r="H25" t="n">
-        <v>4.30986444869051</v>
+        <v>4.280546913967818</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7078644558057595</v>
+        <v>0.7072039367001662</v>
       </c>
       <c r="J25" t="n">
-        <v>6.203690679830312</v>
+        <v>6.110863684376735</v>
       </c>
       <c r="K25" t="n">
-        <v>1.435672142916673</v>
+        <v>1.395350547687038</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7904043980533315</v>
+        <v>0.7943976598076585</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1094419460886547</v>
+        <v>0.1059108698707406</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8431578947368421</v>
+        <v>0.8478947368421053</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06890270853764636</v>
+        <v>0.07138700808945592</v>
       </c>
       <c r="P25" t="n">
-        <v>3.263806773328233</v>
+        <v>3.258874116225943</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3364356840721859</v>
+        <v>0.3435624246141789</v>
       </c>
       <c r="R25" t="n">
-        <v>-97.28259438186711</v>
+        <v>-97.51588070696671</v>
       </c>
       <c r="S25" t="n">
-        <v>7.462666543302724</v>
+        <v>7.504877567857443</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F26" t="n">
         <v>50</v>
@@ -2218,40 +2218,40 @@
         <v>1900</v>
       </c>
       <c r="H26" t="n">
-        <v>3.447887237511382</v>
+        <v>3.375774780228361</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7875371416057402</v>
+        <v>0.7255111194052896</v>
       </c>
       <c r="J26" t="n">
-        <v>5.507973706548642</v>
+        <v>5.349084714321098</v>
       </c>
       <c r="K26" t="n">
-        <v>1.963807214309979</v>
+        <v>1.645171125477299</v>
       </c>
       <c r="L26" t="n">
-        <v>0.827016370056226</v>
+        <v>0.8384849534308451</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1284825610013011</v>
+        <v>0.1023818873599492</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8594736842105264</v>
+        <v>0.8289473684210528</v>
       </c>
       <c r="O26" t="n">
-        <v>0.05540746337425231</v>
+        <v>0.05805806470481389</v>
       </c>
       <c r="P26" t="n">
-        <v>3.009890333438893</v>
+        <v>3.070287747041409</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4527914364730061</v>
+        <v>0.4963363258348464</v>
       </c>
       <c r="R26" t="n">
-        <v>-54.6169184348223</v>
+        <v>-54.83226482951265</v>
       </c>
       <c r="S26" t="n">
-        <v>7.913167714040959</v>
+        <v>7.70887402540654</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F27" t="n">
         <v>50</v>
@@ -2283,40 +2283,40 @@
         <v>1900</v>
       </c>
       <c r="H27" t="n">
-        <v>3.447887275595192</v>
+        <v>3.372599242991528</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7875371510231362</v>
+        <v>0.7213625728310327</v>
       </c>
       <c r="J27" t="n">
-        <v>5.50797380782198</v>
+        <v>5.356006034364061</v>
       </c>
       <c r="K27" t="n">
-        <v>1.963807319298807</v>
+        <v>1.645455832483003</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8270163620847605</v>
+        <v>0.8382019882517224</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1284825693527775</v>
+        <v>0.1022799364734058</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8594736842105264</v>
+        <v>0.8605263157894736</v>
       </c>
       <c r="O27" t="n">
-        <v>0.05540746337425231</v>
+        <v>0.05402296189172899</v>
       </c>
       <c r="P27" t="n">
-        <v>3.009885056327977</v>
+        <v>2.994317943345729</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4527857461033208</v>
+        <v>0.4173663509299333</v>
       </c>
       <c r="R27" t="n">
-        <v>-54.61691843486106</v>
+        <v>-54.86709171451206</v>
       </c>
       <c r="S27" t="n">
-        <v>7.913167714059463</v>
+        <v>7.75310694557309</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F28" t="n">
         <v>50</v>
@@ -2348,40 +2348,40 @@
         <v>1900</v>
       </c>
       <c r="H28" t="n">
-        <v>3.459275160214174</v>
+        <v>3.372599257012384</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8121892375948289</v>
+        <v>0.7213626256790601</v>
       </c>
       <c r="J28" t="n">
-        <v>5.509337043310608</v>
+        <v>5.356006045889773</v>
       </c>
       <c r="K28" t="n">
-        <v>1.952084939048284</v>
+        <v>1.645455687921243</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8272428581145455</v>
+        <v>0.8382019910561094</v>
       </c>
       <c r="M28" t="n">
-        <v>0.125246033848036</v>
+        <v>0.1022799091693006</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8273684210526316</v>
+        <v>0.8605263157894736</v>
       </c>
       <c r="O28" t="n">
-        <v>0.06811880693477368</v>
+        <v>0.05402296189172899</v>
       </c>
       <c r="P28" t="n">
-        <v>3.097379074359492</v>
+        <v>2.994312942399523</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.523679556470001</v>
+        <v>0.4173601342127395</v>
       </c>
       <c r="R28" t="n">
-        <v>-54.52704701592004</v>
+        <v>-54.86709171470655</v>
       </c>
       <c r="S28" t="n">
-        <v>7.920303107969939</v>
+        <v>7.753106945679795</v>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
@@ -2397,14 +2397,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rbf</t>
+          <t>matern_1.5</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1e-06</v>
+        <v>0.01</v>
       </c>
       <c r="F29" t="n">
         <v>50</v>
@@ -2413,40 +2413,40 @@
         <v>1900</v>
       </c>
       <c r="H29" t="n">
-        <v>3.468473355900116</v>
+        <v>3.357886682371592</v>
       </c>
       <c r="I29" t="n">
-        <v>0.803553863307471</v>
+        <v>0.7131247252207706</v>
       </c>
       <c r="J29" t="n">
-        <v>5.528016143051469</v>
+        <v>5.420072556009692</v>
       </c>
       <c r="K29" t="n">
-        <v>1.936064294617601</v>
+        <v>1.639885913294939</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8264153479628094</v>
+        <v>0.8343743216583303</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1246657795469599</v>
+        <v>0.1048558694566506</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8557894736842105</v>
+        <v>0.8263157894736842</v>
       </c>
       <c r="O29" t="n">
-        <v>0.05878141439305884</v>
+        <v>0.06061847931051541</v>
       </c>
       <c r="P29" t="n">
-        <v>3.009765652514613</v>
+        <v>3.082196412834537</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4442078974580527</v>
+        <v>0.4955254578678781</v>
       </c>
       <c r="R29" t="n">
-        <v>-54.51119522962355</v>
+        <v>-53.81904058446682</v>
       </c>
       <c r="S29" t="n">
-        <v>7.912920955870979</v>
+        <v>7.870216284299254</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -2462,14 +2462,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rbf</t>
+          <t>matern_1.5</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F30" t="n">
         <v>50</v>
@@ -2478,40 +2478,40 @@
         <v>1900</v>
       </c>
       <c r="H30" t="n">
-        <v>3.468660819270315</v>
+        <v>3.362952490272983</v>
       </c>
       <c r="I30" t="n">
-        <v>0.790914866690111</v>
+        <v>0.7090264169388196</v>
       </c>
       <c r="J30" t="n">
-        <v>5.538786162479036</v>
+        <v>5.428073178793333</v>
       </c>
       <c r="K30" t="n">
-        <v>1.959574955423372</v>
+        <v>1.630924020065625</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8252038112562962</v>
+        <v>0.8340583718911307</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1282380298588301</v>
+        <v>0.1045508489490338</v>
       </c>
       <c r="N30" t="n">
-        <v>0.8336842105263158</v>
+        <v>0.8547368421052631</v>
       </c>
       <c r="O30" t="n">
-        <v>0.06499303093225356</v>
+        <v>0.05781167755410851</v>
       </c>
       <c r="P30" t="n">
-        <v>3.098044252837302</v>
+        <v>2.99353673944706</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.52910237251472</v>
+        <v>0.4159480555905435</v>
       </c>
       <c r="R30" t="n">
-        <v>-54.75091726418832</v>
+        <v>-53.75051636982636</v>
       </c>
       <c r="S30" t="n">
-        <v>8.105095009580612</v>
+        <v>7.878296062357085</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -2527,14 +2527,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rbf</t>
+          <t>matern_1.5</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1e-10</v>
+        <v>1e-06</v>
       </c>
       <c r="F31" t="n">
         <v>50</v>
@@ -2543,40 +2543,40 @@
         <v>1900</v>
       </c>
       <c r="H31" t="n">
-        <v>3.499069919705792</v>
+        <v>3.362953687708487</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7440163202987629</v>
+        <v>0.7090275254235656</v>
       </c>
       <c r="J31" t="n">
-        <v>5.59619661048285</v>
+        <v>5.428076643239733</v>
       </c>
       <c r="K31" t="n">
-        <v>1.842224595039959</v>
+        <v>1.63092486503835</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8234702003406418</v>
+        <v>0.8340581772537368</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1208181385010656</v>
+        <v>0.1045509049095321</v>
       </c>
       <c r="N31" t="n">
-        <v>0.853157894736842</v>
+        <v>0.8547368421052631</v>
       </c>
       <c r="O31" t="n">
-        <v>0.05993617876931932</v>
+        <v>0.05781167755410851</v>
       </c>
       <c r="P31" t="n">
-        <v>3.023469767367615</v>
+        <v>2.993543248589899</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4385692286954482</v>
+        <v>0.4159544236593705</v>
       </c>
       <c r="R31" t="n">
-        <v>-54.47254933674228</v>
+        <v>-53.75051636901658</v>
       </c>
       <c r="S31" t="n">
-        <v>7.872651852995056</v>
+        <v>7.878296062686805</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -2592,14 +2592,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>matern_1.5</t>
+          <t>rbf</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01</v>
+        <v>1e-10</v>
       </c>
       <c r="F32" t="n">
         <v>50</v>
@@ -2608,40 +2608,40 @@
         <v>1900</v>
       </c>
       <c r="H32" t="n">
-        <v>3.429613100914366</v>
+        <v>3.44483605482529</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7591323062822439</v>
+        <v>0.7209664341614913</v>
       </c>
       <c r="J32" t="n">
-        <v>5.643689651156511</v>
+        <v>5.446421742711656</v>
       </c>
       <c r="K32" t="n">
-        <v>1.87683509332247</v>
+        <v>1.602730747218287</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8196308997603325</v>
+        <v>0.8334970285676591</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1251619386446413</v>
+        <v>0.1023317121213992</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8278947368421053</v>
+        <v>0.8510526315789474</v>
       </c>
       <c r="O32" t="n">
-        <v>0.06450628299710111</v>
+        <v>0.05838819098802408</v>
       </c>
       <c r="P32" t="n">
-        <v>3.081228253668448</v>
+        <v>3.013276536006227</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4565140905803406</v>
+        <v>0.4289708577284528</v>
       </c>
       <c r="R32" t="n">
-        <v>-53.73927493822739</v>
+        <v>-54.60918874275697</v>
       </c>
       <c r="S32" t="n">
-        <v>7.787635462848805</v>
+        <v>7.667598933928912</v>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>matern_1.5</t>
+          <t>rbf</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01</v>
+        <v>1e-06</v>
       </c>
       <c r="F33" t="n">
         <v>50</v>
@@ -2673,40 +2673,40 @@
         <v>1900</v>
       </c>
       <c r="H33" t="n">
-        <v>3.440446096052899</v>
+        <v>3.45855682257341</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7648585014647746</v>
+        <v>0.709346437644061</v>
       </c>
       <c r="J33" t="n">
-        <v>5.64655203064743</v>
+        <v>5.465151823334768</v>
       </c>
       <c r="K33" t="n">
-        <v>1.88594714573904</v>
+        <v>1.586697487549569</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8192593325733032</v>
+        <v>0.8326165242210425</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1257029561095357</v>
+        <v>0.1018263341594471</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8289473684210528</v>
+        <v>0.8505263157894737</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06538544034182737</v>
+        <v>0.05858875109406964</v>
       </c>
       <c r="P33" t="n">
-        <v>3.084886576573993</v>
+        <v>3.016109475361398</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4768533605801636</v>
+        <v>0.4274900597569351</v>
       </c>
       <c r="R33" t="n">
-        <v>-53.66939707665025</v>
+        <v>-54.57895605954977</v>
       </c>
       <c r="S33" t="n">
-        <v>7.845857053903265</v>
+        <v>7.653667896448739</v>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>matern_1.5</t>
+          <t>rbf</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F34" t="n">
         <v>50</v>
@@ -2738,40 +2738,40 @@
         <v>1900</v>
       </c>
       <c r="H34" t="n">
-        <v>3.436332446224732</v>
+        <v>3.448817432492355</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7563266418987965</v>
+        <v>0.6730291939744064</v>
       </c>
       <c r="J34" t="n">
-        <v>5.659836543776469</v>
+        <v>5.471951794460174</v>
       </c>
       <c r="K34" t="n">
-        <v>1.868858499606933</v>
+        <v>1.544686559015644</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8187714039771197</v>
+        <v>0.8329449590765416</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1248289752560844</v>
+        <v>0.09917339540998758</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8542105263157893</v>
+        <v>0.8189473684210529</v>
       </c>
       <c r="O34" t="n">
-        <v>0.05877420091694392</v>
+        <v>0.06460042563612206</v>
       </c>
       <c r="P34" t="n">
-        <v>3.006091634867496</v>
+        <v>3.10403123753315</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.4016435718181773</v>
+        <v>0.4896261721429646</v>
       </c>
       <c r="R34" t="n">
-        <v>-53.63197167737106</v>
+        <v>-54.64522391765543</v>
       </c>
       <c r="S34" t="n">
-        <v>7.843213088450745</v>
+        <v>7.642219094877765</v>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
         <v>1e-06</v>
@@ -2803,40 +2803,40 @@
         <v>1900</v>
       </c>
       <c r="H35" t="n">
-        <v>3.436332599900075</v>
+        <v>3.396178073364758</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7563268730264879</v>
+        <v>0.7169407873639657</v>
       </c>
       <c r="J35" t="n">
-        <v>5.659837462107099</v>
+        <v>5.477859126268156</v>
       </c>
       <c r="K35" t="n">
-        <v>1.868859419004503</v>
+        <v>1.631822415420769</v>
       </c>
       <c r="L35" t="n">
-        <v>0.818771342878918</v>
+        <v>0.8311169301944471</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1248290448309067</v>
+        <v>0.1046640948659288</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8542105263157893</v>
+        <v>0.8531578947368422</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05877420091694392</v>
+        <v>0.05969991098285434</v>
       </c>
       <c r="P35" t="n">
-        <v>3.006098255329228</v>
+        <v>3.007387942759916</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4016483677495769</v>
+        <v>0.4169916726660465</v>
       </c>
       <c r="R35" t="n">
-        <v>-53.63197167465214</v>
+        <v>-53.58137344077632</v>
       </c>
       <c r="S35" t="n">
-        <v>7.843213087692713</v>
+        <v>7.906737794648699</v>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -2859,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>1e-06</v>
+        <v>1e-10</v>
       </c>
       <c r="F36" t="n">
         <v>50</v>
@@ -2868,40 +2868,40 @@
         <v>1900</v>
       </c>
       <c r="H36" t="n">
-        <v>3.457794578556639</v>
+        <v>3.390550478344702</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7569918640948623</v>
+        <v>0.7212641940945085</v>
       </c>
       <c r="J36" t="n">
-        <v>5.682866503474174</v>
+        <v>5.479337827550622</v>
       </c>
       <c r="K36" t="n">
-        <v>1.860206063003446</v>
+        <v>1.623387913362152</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8175384608051202</v>
+        <v>0.8310580946669941</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1247506786415152</v>
+        <v>0.1042535344231667</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8521052631578947</v>
+        <v>0.8526315789473685</v>
       </c>
       <c r="O36" t="n">
-        <v>0.05917680147089036</v>
+        <v>0.05944130940166126</v>
       </c>
       <c r="P36" t="n">
-        <v>3.010248538532638</v>
+        <v>3.005250228188988</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4147124835740001</v>
+        <v>0.4186318922284278</v>
       </c>
       <c r="R36" t="n">
-        <v>-53.54928182938434</v>
+        <v>-53.67014624688863</v>
       </c>
       <c r="S36" t="n">
-        <v>7.915167841919645</v>
+        <v>7.923729991811849</v>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
         <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>1e-10</v>
+        <v>0.01</v>
       </c>
       <c r="F37" t="n">
         <v>50</v>
@@ -2933,40 +2933,40 @@
         <v>1900</v>
       </c>
       <c r="H37" t="n">
-        <v>3.462833937236998</v>
+        <v>3.39285476723357</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7525976023288448</v>
+        <v>0.7217798517832983</v>
       </c>
       <c r="J37" t="n">
-        <v>5.683712899246404</v>
+        <v>5.47982023424492</v>
       </c>
       <c r="K37" t="n">
-        <v>1.859530455790427</v>
+        <v>1.636193870822864</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8174976504668363</v>
+        <v>0.8312882954259142</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1247238303781713</v>
+        <v>0.1040981070045149</v>
       </c>
       <c r="N37" t="n">
-        <v>0.851578947368421</v>
+        <v>0.8226315789473684</v>
       </c>
       <c r="O37" t="n">
-        <v>0.05890630762646884</v>
+        <v>0.06057416499332897</v>
       </c>
       <c r="P37" t="n">
-        <v>3.00884706545734</v>
+        <v>3.094319834721072</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4158906617536172</v>
+        <v>0.4892588024978038</v>
       </c>
       <c r="R37" t="n">
-        <v>-53.53953091286057</v>
+        <v>-53.63823416537296</v>
       </c>
       <c r="S37" t="n">
-        <v>7.909509779012843</v>
+        <v>7.764241896043386</v>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
